--- a/data/incidenti_pedone.xlsx
+++ b/data/incidenti_pedone.xlsx
@@ -15256,7 +15256,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>12A</t>
+          <t>informazione non disponibile</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
